--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MICHIGAN_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MICHIGAN_2014.xlsx
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C173">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C181">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C483">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C534">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C545">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C770">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C839">
